--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 01/09/2026</t>
+As of 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001506012</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242115</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000001506003</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>Mrs. Almina Dhalla</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,431 +722,17 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>240.0</v>
+        <v>300.0</v>
       </c>
       <c r="N3" t="n">
-        <v>240.0</v>
+        <v>300.0</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>510492000001474010</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>242080</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>510492000001474001</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>First Class Learning Reading Central</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>270.0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>270.0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>510492000001477103</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>242081</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>510492000000541229</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Optimum Global Care</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>510492000001482001</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>242082</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>510492000001057001</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Corby Motors Ltd</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>555.0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>555.0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>510492000001482018</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>242083</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>510492000001413024</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>88 DRIVING SCHOOL LTD</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>110.0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>110.0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>510492000001488015</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>242084</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>510492000001488006</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>SPOT CLEANERS LTD</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>130.0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>130.0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>510492000001367115</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>242017</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>510492000001025001</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>310.3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>310.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1155,7 +741,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A4:O4"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 09/09/2026</t>
+As of 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001506012</t>
+          <t>510492000001514001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242115</t>
+          <t>242119</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000001506003</t>
+          <t>510492000001378001</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Mrs. Almina Dhalla</t>
+          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,17 +722,362 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>300.0</v>
+        <v>540.0</v>
       </c>
       <c r="N3" t="n">
-        <v>300.0</v>
+        <v>540.0</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="55" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>510492000001517010</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>242120</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>510492000001517001</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Max Out Tutoring</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>480.0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>480.0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>510492000001517029</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>242121</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>510492000001517001</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Max Out Tutoring</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>480.0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>480.0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>510492000001517056</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>242122</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>510492000001088061</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Drive with Greta</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>510492000001517086</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>242124</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>510492000001260001</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Elite Learning Epsom Ltd</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="N7" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>510492000001517103</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>242125</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>510492000001391001</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>PAVS DRIVING SCHOOL</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="N8" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -741,7 +1086,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A9:O9"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 16/09/2026</t>
+As of 18/09/2026</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001514001</t>
+          <t>510492000001517029</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242119</t>
+          <t>242121</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000001378001</t>
+          <t>510492000001517001</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
+          <t>Max Out Tutoring</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>540.0</v>
+        <v>480.0</v>
       </c>
       <c r="N3" t="n">
-        <v>540.0</v>
+        <v>480.0</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
@@ -734,7 +734,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>510492000001517010</t>
+          <t>510492000001517056</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>242120</t>
+          <t>242122</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>510492000001517001</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Max Out Tutoring</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>480.0</v>
+        <v>28.8</v>
       </c>
       <c r="N4" t="n">
-        <v>480.0</v>
+        <v>28.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.0</v>
@@ -803,7 +803,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>510492000001517029</t>
+          <t>510492000001517086</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -841,17 +841,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>242121</t>
+          <t>242124</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>510492000001517001</t>
+          <t>510492000001260001</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Max Out Tutoring</t>
+          <t>Elite Learning Epsom Ltd</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>480.0</v>
+        <v>57.24</v>
       </c>
       <c r="N5" t="n">
-        <v>480.0</v>
+        <v>57.24</v>
       </c>
       <c r="O5" t="n">
         <v>1.0</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>510492000001517056</t>
+          <t>510492000001517103</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -910,17 +910,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>242122</t>
+          <t>242125</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001391001</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>PAVS DRIVING SCHOOL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>28.8</v>
+        <v>18.96</v>
       </c>
       <c r="N6" t="n">
-        <v>28.8</v>
+        <v>18.96</v>
       </c>
       <c r="O6" t="n">
         <v>1.0</v>
@@ -951,7 +951,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>510492000001517086</t>
+          <t>510492000001517128</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -979,17 +979,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>242124</t>
+          <t>242127</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>510492000001260001</t>
+          <t>510492000001025001</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Elite Learning Epsom Ltd</t>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>57.24</v>
+        <v>375.0</v>
       </c>
       <c r="N7" t="n">
-        <v>57.24</v>
+        <v>375.0</v>
       </c>
       <c r="O7" t="n">
         <v>1.0</v>
@@ -1010,7 +1010,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>510492000001517103</t>
+          <t>510492000001527001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1048,17 +1048,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>242125</t>
+          <t>242128</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>510492000001391001</t>
+          <t>510492000000256001</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>PAVS DRIVING SCHOOL</t>
+          <t>OPTIMUM GLOBAL LINKS</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>18.96</v>
+        <v>120.0</v>
       </c>
       <c r="N8" t="n">
-        <v>18.96</v>
+        <v>120.0</v>
       </c>
       <c r="O8" t="n">
         <v>1.0</v>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>partially_paid</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>510492000001517103</t>
+          <t>510492000001517128</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -910,17 +910,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>242125</t>
+          <t>242127</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>510492000001391001</t>
+          <t>510492000001025001</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>PAVS DRIVING SCHOOL</t>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>18.96</v>
+        <v>125.0</v>
       </c>
       <c r="N6" t="n">
-        <v>18.96</v>
+        <v>375.0</v>
       </c>
       <c r="O6" t="n">
         <v>1.0</v>
@@ -941,7 +941,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>510492000001517128</t>
+          <t>510492000001527001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -979,17 +979,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>242127</t>
+          <t>242128</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>510492000001025001</t>
+          <t>510492000000256001</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+          <t>OPTIMUM GLOBAL LINKS</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -998,86 +998,17 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>375.0</v>
+        <v>120.0</v>
       </c>
       <c r="N7" t="n">
-        <v>375.0</v>
+        <v>120.0</v>
       </c>
       <c r="O7" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>510492000001527001</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>242128</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>510492000000256001</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>OPTIMUM GLOBAL LINKS</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="55" t="inlineStr">
+      <c r="A8" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1086,7 +1017,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="A8:O8"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 18/09/2026</t>
+As of 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001517029</t>
+          <t>510492000001531197</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242121</t>
+          <t>242129</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000001517001</t>
+          <t>510492000001531188</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Max Out Tutoring</t>
+          <t>Kumon North Harrow</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>480.0</v>
+        <v>240.0</v>
       </c>
       <c r="N3" t="n">
-        <v>480.0</v>
+        <v>240.0</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
@@ -734,7 +734,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>510492000001517056</t>
+          <t>510492000001531223</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>242122</t>
+          <t>242130</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001531214</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>Kumon Harrow South</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>28.8</v>
+        <v>240.0</v>
       </c>
       <c r="N4" t="n">
-        <v>28.8</v>
+        <v>240.0</v>
       </c>
       <c r="O4" t="n">
         <v>1.0</v>
@@ -803,7 +803,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>510492000001517086</t>
+          <t>510492000001540001</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -841,17 +841,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>242124</t>
+          <t>242131</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>510492000001260001</t>
+          <t>510492000001450146</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Elite Learning Epsom Ltd</t>
+          <t>Mr. Phone Mobile &amp; Vape</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>57.24</v>
+        <v>240.0</v>
       </c>
       <c r="N5" t="n">
-        <v>57.24</v>
+        <v>240.0</v>
       </c>
       <c r="O5" t="n">
         <v>1.0</v>
@@ -872,17 +872,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>partially_paid</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>510492000001517128</t>
+          <t>510492000001543001</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -910,17 +910,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>242127</t>
+          <t>242132</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>510492000001025001</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -929,86 +929,17 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>125.0</v>
+        <v>400.0</v>
       </c>
       <c r="N6" t="n">
-        <v>375.0</v>
+        <v>400.0</v>
       </c>
       <c r="O6" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>510492000001527001</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>242128</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>510492000000256001</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>OPTIMUM GLOBAL LINKS</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1017,7 +948,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="A7:O7"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 23/09/2026</t>
+As of 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -665,17 +665,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>partially_paid</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001531197</t>
+          <t>510492000001540001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242129</t>
+          <t>242131</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000001531188</t>
+          <t>510492000001450146</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Kumon North Harrow</t>
+          <t>Mr. Phone Mobile &amp; Vape</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>240.0</v>
+        <v>120.0</v>
       </c>
       <c r="N3" t="n">
         <v>240.0</v>
@@ -734,7 +734,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>510492000001531223</t>
+          <t>510492000001543001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>242130</t>
+          <t>242132</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>510492000001531214</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Kumon Harrow South</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>240.0</v>
+        <v>400.0</v>
       </c>
       <c r="N4" t="n">
-        <v>240.0</v>
+        <v>400.0</v>
       </c>
       <c r="O4" t="n">
         <v>1.0</v>
@@ -803,7 +803,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>510492000001540001</t>
+          <t>510492000001543036</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -841,17 +841,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>242131</t>
+          <t>242133</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>510492000001450146</t>
+          <t>510492000001543027</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Mr. Phone Mobile &amp; Vape</t>
+          <t>MRB ELITE PROTECTION &amp; MAINTENANCE LTD</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -860,86 +860,17 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>240.0</v>
+        <v>420.0</v>
       </c>
       <c r="N5" t="n">
-        <v>240.0</v>
+        <v>420.0</v>
       </c>
       <c r="O5" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>510492000001543001</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>242132</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>510492000000327139</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>BATHROOMS LONDON LIMITED</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>400.0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>400.0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -948,7 +879,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A7:O7"/>
+    <mergeCell ref="A6:O6"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 25/09/2026</t>
+As of 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -665,17 +665,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>partially_paid</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001540001</t>
+          <t>510492000001566001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242131</t>
+          <t>242138</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000001450146</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Mr. Phone Mobile &amp; Vape</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="N3" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
@@ -734,7 +734,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>510492000001543001</t>
+          <t>510492000001566037</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>242132</t>
+          <t>242140</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>510492000000327139</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>BATHROOMS LONDON LIMITED</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>400.0</v>
+        <v>238.8</v>
       </c>
       <c r="N4" t="n">
-        <v>400.0</v>
+        <v>238.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.0</v>
@@ -803,7 +803,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>510492000001543036</t>
+          <t>510492000001566055</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -841,17 +841,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>242133</t>
+          <t>242141</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>510492000001543027</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>MRB ELITE PROTECTION &amp; MAINTENANCE LTD</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -860,17 +860,362 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>420.0</v>
+        <v>477.6</v>
       </c>
       <c r="N5" t="n">
-        <v>420.0</v>
+        <v>477.6</v>
       </c>
       <c r="O5" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>510492000001566074</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>242142</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>510492000000192073</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SUPERHOUSE (UK) LIMITED</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>510492000001566182</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>242148</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>510492000000505059</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Chorus Music Therapy &amp; Education</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>510492000001566254</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>242152</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>510492000000742001</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Adam’s Painting and Decorating</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>510492000001566380</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>242159</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>510492000001573069</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>242165</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>510492000001155001</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Galloway Pest Control</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>360.0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>360.0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -879,7 +1224,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A11:O11"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 05/10/2026</t>
+As of 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001566001</t>
+          <t>510492000001582047</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242138</t>
+          <t>242168</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000001582038</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>CONNECT DRIVING SCHOOL LIMITED</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>238.8</v>
+        <v>620.0</v>
       </c>
       <c r="N3" t="n">
-        <v>238.8</v>
+        <v>620.0</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
@@ -734,7 +734,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>510492000001566037</t>
+          <t>510492000001582076</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>242140</t>
+          <t>242169</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000001582067</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>BOILER GAS TECH LIMITED</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -791,431 +791,17 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>238.8</v>
+        <v>100.0</v>
       </c>
       <c r="N4" t="n">
-        <v>238.8</v>
+        <v>100.0</v>
       </c>
       <c r="O4" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>510492000001566055</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>242141</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>510492000000123277</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Patrick Shoes Limited</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>477.6</v>
-      </c>
-      <c r="N5" t="n">
-        <v>477.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>510492000001566074</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>242142</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>510492000000192073</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>238.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>238.8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>510492000001566182</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>242148</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>510492000000505059</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Chorus Music Therapy &amp; Education</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>510492000001566254</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>242152</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>510492000000742001</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Adam’s Painting and Decorating</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>510492000001566380</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>242159</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>510492000000123277</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Patrick Shoes Limited</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>510492000001573069</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>242165</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>510492000001155001</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Galloway Pest Control</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>360.0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>360.0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="55" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1224,7 +810,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="A5:O5"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 07/10/2026</t>
+As of 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>partially_paid</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>620.0</v>
+        <v>370.0</v>
       </c>
       <c r="N3" t="n">
         <v>620.0</v>
@@ -734,7 +734,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>510492000001582076</t>
+          <t>510492000001587077</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>242169</t>
+          <t>242170</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>510492000001582067</t>
+          <t>510492000001025001</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>BOILER GAS TECH LIMITED</t>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>100.0</v>
+        <v>354.0</v>
       </c>
       <c r="N4" t="n">
-        <v>100.0</v>
+        <v>354.0</v>
       </c>
       <c r="O4" t="n">
         <v>1.0</v>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 09/10/2026</t>
+As of 14/10/2026</t>
         </is>
       </c>
     </row>
@@ -665,17 +665,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>partially_paid</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001582047</t>
+          <t>510492000001591001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242168</t>
+          <t>242171</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000001582038</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>CONNECT DRIVING SCHOOL LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,86 +722,17 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>370.0</v>
+        <v>132.0</v>
       </c>
       <c r="N3" t="n">
-        <v>620.0</v>
+        <v>132.0</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>510492000001587077</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>242170</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>510492000001025001</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>354.0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>354.0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="55" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -810,7 +741,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A4:O4"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 14/10/2026</t>
+As of 28/10/2026</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001591001</t>
+          <t>510492000001617001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242171</t>
+          <t>242175</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001582038</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>CONNECT DRIVING SCHOOL LIMITED</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,17 +722,155 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>132.0</v>
+        <v>480.0</v>
       </c>
       <c r="N3" t="n">
-        <v>132.0</v>
+        <v>480.0</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="55" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>510492000001617021</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>242176</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>510492000001517001</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Max Out Tutoring</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>360.0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>360.0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>510492000001631150</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>242179</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>510492000000327139</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>BATHROOMS LONDON LIMITED</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>260.0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>260.0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -741,7 +879,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A6:O6"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_current_zoho.xlsx
+++ b/AR_current_zoho.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -51,6 +51,11 @@
     </font>
     <font>
       <name val="arial"/>
+      <sz val="10.0"/>
+      <color rgb="FF666666"/>
+    </font>
+    <font>
+      <name val="arial"/>
       <sz val="12.0"/>
       <color rgb="FF000000"/>
       <b val="true"/>
@@ -93,6 +98,11 @@
       <color rgb="FF000000"/>
       <b val="true"/>
       <i val="true"/>
+    </font>
+    <font>
+      <name val="arial"/>
+      <sz val="10.0"/>
+      <color rgb="FF666666"/>
     </font>
     <font>
       <name val="arial"/>
@@ -293,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -301,253 +311,271 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -556,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -577,11 +605,11 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" ht="70.0">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 28/10/2026</t>
+As of 31/10/2026</t>
         </is>
       </c>
     </row>
@@ -665,7 +693,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +703,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>510492000001617001</t>
+          <t>510492000001631150</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -690,7 +718,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -703,17 +731,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242175</t>
+          <t>242179</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>510492000001582038</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>CONNECT DRIVING SCHOOL LIMITED</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,155 +750,17 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>480.0</v>
+        <v>260.0</v>
       </c>
       <c r="N3" t="n">
-        <v>480.0</v>
+        <v>260.0</v>
       </c>
       <c r="O3" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>510492000001617021</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>242176</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>510492000001517001</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Max Out Tutoring</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>360.0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>360.0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>510492000001631150</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>242179</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>510492000000327139</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>BATHROOMS LONDON LIMITED</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>260.0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>260.0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -879,7 +769,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A4:O4"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
